--- a/test-docs/collections/cron/cron.xlsx
+++ b/test-docs/collections/cron/cron.xlsx
@@ -11,7 +11,7 @@
     <sheet name="COL-cron" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'COL-cron'!$A$4:$F$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'COL-cron'!$A$4:$F$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1443,7 +1443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1463,7 +1463,7 @@
     <row r="2">
       <c r="A2" s="13" t="inlineStr">
         <is>
-          <t>COL-cron — Curated Test Collection (active; 68 TCs referenced; vacation s135 + reports s136 + cross-service s137)</t>
+          <t>COL-cron — Curated Test Collection (complete; 87 TCs referenced; vacation s135 + reports s136 + cross-service s137 + statistics + email s138)</t>
         </is>
       </c>
     </row>
@@ -3675,8 +3675,616 @@
         </is>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" s="15" t="inlineStr">
+        <is>
+          <t>TC-STAT-077</t>
+        </is>
+      </c>
+      <c r="B73" s="15" t="inlineStr">
+        <is>
+          <t>statistics</t>
+        </is>
+      </c>
+      <c r="C73" s="15" t="inlineStr">
+        <is>
+          <t>TS-Stat-CronStatReportSync</t>
+        </is>
+      </c>
+      <c r="D73" s="15" t="inlineStr">
+        <is>
+          <t>StatisticReportScheduler — cron fires at 04:00 NSK, ShedLock acquired/released, start/finish markers emit</t>
+        </is>
+      </c>
+      <c r="E73" s="15" t="inlineStr">
+        <is>
+          <t>Row 22 happy-path; baseline periodic sync with ShedLock</t>
+        </is>
+      </c>
+      <c r="F73" s="15" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="16" t="inlineStr">
+        <is>
+          <t>TC-STAT-078</t>
+        </is>
+      </c>
+      <c r="B74" s="16" t="inlineStr">
+        <is>
+          <t>statistics</t>
+        </is>
+      </c>
+      <c r="C74" s="16" t="inlineStr">
+        <is>
+          <t>TS-Stat-CronStatReportSync</t>
+        </is>
+      </c>
+      <c r="D74" s="16" t="inlineStr">
+        <is>
+          <t>Delta #8 regression — statistic-report sync failure logged at INFO (level:6), NOT ERROR (level:3)</t>
+        </is>
+      </c>
+      <c r="E74" s="16" t="inlineStr">
+        <is>
+          <t>Row 22 design issue; delta #8 log-level regression guard</t>
+        </is>
+      </c>
+      <c r="F74" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="15" t="inlineStr">
+        <is>
+          <t>TC-STAT-079</t>
+        </is>
+      </c>
+      <c r="B75" s="15" t="inlineStr">
+        <is>
+          <t>statistics</t>
+        </is>
+      </c>
+      <c r="C75" s="15" t="inlineStr">
+        <is>
+          <t>TS-Stat-CronStatReportSync</t>
+        </is>
+      </c>
+      <c r="D75" s="15" t="inlineStr">
+        <is>
+          <t>#3345 Bug 1 regression — employment-period filter excludes pre-hire and post-leave months</t>
+        </is>
+      </c>
+      <c r="E75" s="15" t="inlineStr">
+        <is>
+          <t>Row 22 regression; #3345 MR !5101 fix</t>
+        </is>
+      </c>
+      <c r="F75" s="15" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="16" t="inlineStr">
+        <is>
+          <t>TC-STAT-080</t>
+        </is>
+      </c>
+      <c r="B76" s="16" t="inlineStr">
+        <is>
+          <t>statistics</t>
+        </is>
+      </c>
+      <c r="C76" s="16" t="inlineStr">
+        <is>
+          <t>TS-Stat-CronStatReportSync</t>
+        </is>
+      </c>
+      <c r="D76" s="16" t="inlineStr">
+        <is>
+          <t>#3345 Bug 2 regression — day-off reschedule triggers month_norm recalc via RabbitMQ event</t>
+        </is>
+      </c>
+      <c r="E76" s="16" t="inlineStr">
+        <is>
+          <t>Row 22 regression; #3345 event-fan-out fix</t>
+        </is>
+      </c>
+      <c r="F76" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="15" t="inlineStr">
+        <is>
+          <t>TC-STAT-081</t>
+        </is>
+      </c>
+      <c r="B77" s="15" t="inlineStr">
+        <is>
+          <t>statistics</t>
+        </is>
+      </c>
+      <c r="C77" s="15" t="inlineStr">
+        <is>
+          <t>TS-Stat-CronStatReportSync</t>
+        </is>
+      </c>
+      <c r="D77" s="15" t="inlineStr">
+        <is>
+          <t>#3337 regression — sick-leave creation updates month_norm and reported_effort via SICK_LEAVE_CHANGES event</t>
+        </is>
+      </c>
+      <c r="E77" s="15" t="inlineStr">
+        <is>
+          <t>Row 22 regression; #3337 event-enum broadening</t>
+        </is>
+      </c>
+      <c r="F77" s="15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="16" t="inlineStr">
+        <is>
+          <t>TC-STAT-082</t>
+        </is>
+      </c>
+      <c r="B78" s="16" t="inlineStr">
+        <is>
+          <t>statistics</t>
+        </is>
+      </c>
+      <c r="C78" s="16" t="inlineStr">
+        <is>
+          <t>TS-Stat-CronStatReportSync</t>
+        </is>
+      </c>
+      <c r="D78" s="16" t="inlineStr">
+        <is>
+          <t>#3337 regression — scoped event for employee A does NOT delete statistic_report rows for employee B</t>
+        </is>
+      </c>
+      <c r="E78" s="16" t="inlineStr">
+        <is>
+          <t>Row 22 regression; #3337 scoped-delete fix</t>
+        </is>
+      </c>
+      <c r="F78" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="15" t="inlineStr">
+        <is>
+          <t>TC-STAT-083</t>
+        </is>
+      </c>
+      <c r="B79" s="15" t="inlineStr">
+        <is>
+          <t>statistics</t>
+        </is>
+      </c>
+      <c r="C79" s="15" t="inlineStr">
+        <is>
+          <t>TS-Stat-CronStatReportSync</t>
+        </is>
+      </c>
+      <c r="D79" s="15" t="inlineStr">
+        <is>
+          <t>#3346 regression (bug #895498) — manual statistic_report row delete is restored on next optimized sync</t>
+        </is>
+      </c>
+      <c r="E79" s="15" t="inlineStr">
+        <is>
+          <t>Row 22 regression; #3346 scheduler-wiring fix</t>
+        </is>
+      </c>
+      <c r="F79" s="15" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="16" t="inlineStr">
+        <is>
+          <t>TC-STAT-084</t>
+        </is>
+      </c>
+      <c r="B80" s="16" t="inlineStr">
+        <is>
+          <t>statistics</t>
+        </is>
+      </c>
+      <c r="C80" s="16" t="inlineStr">
+        <is>
+          <t>TS-Stat-CronStatReportSync</t>
+        </is>
+      </c>
+      <c r="D80" s="16" t="inlineStr">
+        <is>
+          <t>Full vs optimized sync contract — full refreshes previous + current year; optimized refreshes previous + current month only</t>
+        </is>
+      </c>
+      <c r="E80" s="16" t="inlineStr">
+        <is>
+          <t>Row 22 endpoint-contract; #3345 note 894873</t>
+        </is>
+      </c>
+      <c r="F80" s="16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="15" t="inlineStr">
+        <is>
+          <t>TC-EMAIL-001</t>
+        </is>
+      </c>
+      <c r="B81" s="15" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C81" s="15" t="inlineStr">
+        <is>
+          <t>TS-Email-CronDispatch</t>
+        </is>
+      </c>
+      <c r="D81" s="15" t="inlineStr">
+        <is>
+          <t>EmailSendScheduler — cron fires every 20 s, ShedLock acquired/released, start/finish markers emit</t>
+        </is>
+      </c>
+      <c r="E81" s="15" t="inlineStr">
+        <is>
+          <t>Row 8 happy-path; baseline dispatcher cadence + lock</t>
+        </is>
+      </c>
+      <c r="F81" s="15" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="16" t="inlineStr">
+        <is>
+          <t>TC-EMAIL-002</t>
+        </is>
+      </c>
+      <c r="B82" s="16" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C82" s="16" t="inlineStr">
+        <is>
+          <t>TS-Email-CronDispatch</t>
+        </is>
+      </c>
+      <c r="D82" s="16" t="inlineStr">
+        <is>
+          <t>Dispatch — NEW email transitions to SENT after SMTP success (happy path)</t>
+        </is>
+      </c>
+      <c r="E82" s="16" t="inlineStr">
+        <is>
+          <t>Row 8 SMTP-success status transition</t>
+        </is>
+      </c>
+      <c r="F82" s="16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="15" t="inlineStr">
+        <is>
+          <t>TC-EMAIL-003</t>
+        </is>
+      </c>
+      <c r="B83" s="15" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C83" s="15" t="inlineStr">
+        <is>
+          <t>TS-Email-CronDispatch</t>
+        </is>
+      </c>
+      <c r="D83" s="15" t="inlineStr">
+        <is>
+          <t>Dispatch — invalid recipient transitions NEW → INVALID (SendFailedException path)</t>
+        </is>
+      </c>
+      <c r="E83" s="15" t="inlineStr">
+        <is>
+          <t>Row 8 invalid-recipient status transition</t>
+        </is>
+      </c>
+      <c r="F83" s="15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="16" t="inlineStr">
+        <is>
+          <t>TC-EMAIL-004</t>
+        </is>
+      </c>
+      <c r="B84" s="16" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C84" s="16" t="inlineStr">
+        <is>
+          <t>TS-Email-CronDispatch</t>
+        </is>
+      </c>
+      <c r="D84" s="16" t="inlineStr">
+        <is>
+          <t>Dispatch — partial SMTP failure sets FAILED for rejected messages, SENT for accepted</t>
+        </is>
+      </c>
+      <c r="E84" s="16" t="inlineStr">
+        <is>
+          <t>Row 8 mixed-batch status transitions; DI-EMAIL-DISPATCH-RETRY context</t>
+        </is>
+      </c>
+      <c r="F84" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="15" t="inlineStr">
+        <is>
+          <t>TC-EMAIL-005</t>
+        </is>
+      </c>
+      <c r="B85" s="15" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C85" s="15" t="inlineStr">
+        <is>
+          <t>TS-Email-CronDispatch</t>
+        </is>
+      </c>
+      <c r="D85" s="15" t="inlineStr">
+        <is>
+          <t>DI-EMAIL-DISPATCH-AUTH regression — MailAuthenticationException caught, status NOT updated, infinite retry loop</t>
+        </is>
+      </c>
+      <c r="E85" s="15" t="inlineStr">
+        <is>
+          <t>Row 8 design-issue regression guard; stuck-as-NEW infinite loop</t>
+        </is>
+      </c>
+      <c r="F85" s="15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="16" t="inlineStr">
+        <is>
+          <t>TC-EMAIL-006</t>
+        </is>
+      </c>
+      <c r="B86" s="16" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C86" s="16" t="inlineStr">
+        <is>
+          <t>TS-Email-CronDispatch</t>
+        </is>
+      </c>
+      <c r="D86" s="16" t="inlineStr">
+        <is>
+          <t>Dispatch — pageSize = 300 caps per-batch dispatch; overflow drains in subsequent ticks</t>
+        </is>
+      </c>
+      <c r="E86" s="16" t="inlineStr">
+        <is>
+          <t>Row 8 batch-size contract; pagination window</t>
+        </is>
+      </c>
+      <c r="F86" s="16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="15" t="inlineStr">
+        <is>
+          <t>TC-EMAIL-007</t>
+        </is>
+      </c>
+      <c r="B87" s="15" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C87" s="15" t="inlineStr">
+        <is>
+          <t>TS-Email-CronPrune</t>
+        </is>
+      </c>
+      <c r="D87" s="15" t="inlineStr">
+        <is>
+          <t>EmailPruneScheduler — cron fires daily at 00:00, ShedLock acquired/released, start/finish markers emit</t>
+        </is>
+      </c>
+      <c r="E87" s="15" t="inlineStr">
+        <is>
+          <t>Row 9 happy-path; baseline retention scheduler</t>
+        </is>
+      </c>
+      <c r="F87" s="15" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="16" t="inlineStr">
+        <is>
+          <t>TC-EMAIL-008</t>
+        </is>
+      </c>
+      <c r="B88" s="16" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C88" s="16" t="inlineStr">
+        <is>
+          <t>TS-Email-CronPrune</t>
+        </is>
+      </c>
+      <c r="D88" s="16" t="inlineStr">
+        <is>
+          <t>Retention — emails older than 30 days deleted, emails newer than 30 days preserved</t>
+        </is>
+      </c>
+      <c r="E88" s="16" t="inlineStr">
+        <is>
+          <t>Row 9 retention baseline; PT30D cutoff</t>
+        </is>
+      </c>
+      <c r="F88" s="16" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="15" t="inlineStr">
+        <is>
+          <t>TC-EMAIL-009</t>
+        </is>
+      </c>
+      <c r="B89" s="15" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C89" s="15" t="inlineStr">
+        <is>
+          <t>TS-Email-CronPrune</t>
+        </is>
+      </c>
+      <c r="D89" s="15" t="inlineStr">
+        <is>
+          <t>Retention boundary — email exactly at 30-day cutoff behavior (strict less-than: &lt;30d preserved, =30d deleted)</t>
+        </is>
+      </c>
+      <c r="E89" s="15" t="inlineStr">
+        <is>
+          <t>Row 9 off-by-one guard on strict less-than ADD_TIME.lessThan</t>
+        </is>
+      </c>
+      <c r="F89" s="15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="16" t="inlineStr">
+        <is>
+          <t>TC-EMAIL-010</t>
+        </is>
+      </c>
+      <c r="B90" s="16" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C90" s="16" t="inlineStr">
+        <is>
+          <t>TS-Email-CronPrune</t>
+        </is>
+      </c>
+      <c r="D90" s="16" t="inlineStr">
+        <is>
+          <t>Retention — attachments deleted with parent email (no FK orphans)</t>
+        </is>
+      </c>
+      <c r="E90" s="16" t="inlineStr">
+        <is>
+          <t>Row 9 cascade-delete contract; zero orphans</t>
+        </is>
+      </c>
+      <c r="F90" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="15" t="inlineStr">
+        <is>
+          <t>TC-EMAIL-011</t>
+        </is>
+      </c>
+      <c r="B91" s="15" t="inlineStr">
+        <is>
+          <t>email</t>
+        </is>
+      </c>
+      <c r="C91" s="15" t="inlineStr">
+        <is>
+          <t>TS-Email-CronPrune</t>
+        </is>
+      </c>
+      <c r="D91" s="15" t="inlineStr">
+        <is>
+          <t>Retention no-op — all emails within retention window; finish marker reports 0 deleted</t>
+        </is>
+      </c>
+      <c r="E91" s="15" t="inlineStr">
+        <is>
+          <t>Row 9 no-op idempotency; zero-delete path</t>
+        </is>
+      </c>
+      <c r="F91" s="15" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:F72"/>
+  <autoFilter ref="A4:F91"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A5:F5"/>

--- a/test-docs/collections/cron/cron.xlsx
+++ b/test-docs/collections/cron/cron.xlsx
@@ -11,7 +11,7 @@
     <sheet name="COL-cron" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'COL-cron'!$A$4:$F$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'COL-cron'!$A$4:$G$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1443,15 +1443,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F91"/>
+  <dimension ref="A1:G91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="48" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1463,7 +1464,7 @@
     <row r="2">
       <c r="A2" s="13" t="inlineStr">
         <is>
-          <t>COL-cron — Curated Test Collection (complete; 87 TCs referenced; vacation s135 + reports s136 + cross-service s137 + statistics + email s138)</t>
+          <t>COL-cron — Curated Test Collection (complete; 87 TCs referenced; per-domain Cron_&lt;Domain&gt;.xlsx workbooks under test-docs/collections/cron/)</t>
         </is>
       </c>
     </row>
@@ -1480,20 +1481,25 @@
       </c>
       <c r="C4" s="14" t="inlineStr">
         <is>
+          <t>source_workbook</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
           <t>source_suite</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="F4" s="14" t="inlineStr">
         <is>
           <t>inclusion_reason</t>
         </is>
       </c>
-      <c r="F4" s="14" t="inlineStr">
+      <c r="G4" s="14" t="inlineStr">
         <is>
           <t>priority_override</t>
         </is>
@@ -1512,20 +1518,25 @@
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Vacation.xlsx</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
           <t>TS-Vac-Cron-AnnualAccruals</t>
         </is>
       </c>
-      <c r="D5" s="15" t="inlineStr">
+      <c r="E5" s="15" t="inlineStr">
         <is>
           <t>Annual accruals — clock at 01 Jan advances balances for all enabled employees</t>
         </is>
       </c>
-      <c r="E5" s="15" t="inlineStr">
+      <c r="F5" s="15" t="inlineStr">
         <is>
           <t>Row 11 happy-path; baseline accrual run</t>
         </is>
       </c>
-      <c r="F5" s="15" t="inlineStr">
+      <c r="G5" s="15" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -1544,20 +1555,25 @@
       </c>
       <c r="C6" s="16" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Vacation.xlsx</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
           <t>TS-Vac-Cron-AnnualAccruals</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>Annual accruals — disabled employees excluded from accrual run</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="F6" s="16" t="inlineStr">
         <is>
           <t>Row 11 negative; ensures enabled=true filter</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="G6" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1576,20 +1592,25 @@
       </c>
       <c r="C7" s="15" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Vacation.xlsx</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="inlineStr">
+        <is>
           <t>TS-Vac-Cron-AnnualAccruals</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
+      <c r="E7" s="15" t="inlineStr">
         <is>
           <t>Annual accruals — idempotent on second trigger within same year</t>
         </is>
       </c>
-      <c r="E7" s="15" t="inlineStr">
+      <c r="F7" s="15" t="inlineStr">
         <is>
           <t>Row 11 idempotency; silent-failure guard</t>
         </is>
       </c>
-      <c r="F7" s="15" t="inlineStr">
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1608,20 +1629,25 @@
       </c>
       <c r="C8" s="16" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Vacation.xlsx</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
           <t>TS-Vac-Cron-NotImpl</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>Row 12 stub endpoint returns 200 / 204 with no side effects</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>Row 12 dead-config confirmation</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="G8" s="16" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -1640,20 +1666,25 @@
       </c>
       <c r="C9" s="15" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Vacation.xlsx</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
           <t>TS-Vac-Cron-NotImpl</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="E9" s="15" t="inlineStr">
         <is>
           <t>Row 13 stub endpoint returns 200 / 204 with no side effects</t>
         </is>
       </c>
-      <c r="E9" s="15" t="inlineStr">
+      <c r="F9" s="15" t="inlineStr">
         <is>
           <t>Row 13 dead-config confirmation</t>
         </is>
       </c>
-      <c r="F9" s="15" t="inlineStr">
+      <c r="G9" s="15" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -1672,20 +1703,25 @@
       </c>
       <c r="C10" s="16" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Vacation.xlsx</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
           <t>TS-Vac-Cron-Digest</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>Vacation digest — all employees with upcoming vacation receive single digest email</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>Row 14 happy-path; batch dispatch via email service</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="G10" s="16" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -1704,20 +1740,25 @@
       </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Vacation.xlsx</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
           <t>TS-Vac-Cron-Digest</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="E11" s="15" t="inlineStr">
         <is>
           <t>Vacation digest — employees without upcoming vacation do not receive digest</t>
         </is>
       </c>
-      <c r="E11" s="15" t="inlineStr">
+      <c r="F11" s="15" t="inlineStr">
         <is>
           <t>Row 14 filter; ensures non-empty-only recipients</t>
         </is>
       </c>
-      <c r="F11" s="15" t="inlineStr">
+      <c r="G11" s="15" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1736,20 +1777,25 @@
       </c>
       <c r="C12" s="16" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Vacation.xlsx</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="inlineStr">
+        <is>
           <t>TS-Vac-Cron-Digest</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t>Vacation digest — idempotent on second trigger within same day</t>
         </is>
       </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t>Row 14 idempotency; ShedLock window guard</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="G12" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1768,20 +1814,25 @@
       </c>
       <c r="C13" s="15" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Vacation.xlsx</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
           <t>TS-Vac-Cron-CalendarReminder</t>
         </is>
       </c>
-      <c r="D13" s="15" t="inlineStr">
+      <c r="E13" s="15" t="inlineStr">
         <is>
           <t>Production-calendar annual-first reminder — per-recipient mail to target audience</t>
         </is>
       </c>
-      <c r="E13" s="15" t="inlineStr">
+      <c r="F13" s="15" t="inlineStr">
         <is>
           <t>Row 15 happy-path via test endpoint (scheduler-wrapper bypass)</t>
         </is>
       </c>
-      <c r="F13" s="15" t="inlineStr">
+      <c r="G13" s="15" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -1800,20 +1851,25 @@
       </c>
       <c r="C14" s="16" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Vacation.xlsx</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="inlineStr">
+        <is>
           <t>TS-Vac-Cron-CalendarReminder</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="E14" s="16" t="inlineStr">
         <is>
           <t>Production-calendar reminder — email subject matches NOTIFY_VACATION_CALENDAR_NEXT_YEAR_FIRST template</t>
         </is>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="F14" s="16" t="inlineStr">
         <is>
           <t>Row 15 template verification per delta #5</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="G14" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1832,20 +1888,25 @@
       </c>
       <c r="C15" s="15" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Vacation.xlsx</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
           <t>TS-Vac-Cron-CalendarReminder</t>
         </is>
       </c>
-      <c r="D15" s="15" t="inlineStr">
+      <c r="E15" s="15" t="inlineStr">
         <is>
           <t>Production-calendar reminder — inactive employees excluded from recipient list</t>
         </is>
       </c>
-      <c r="E15" s="15" t="inlineStr">
+      <c r="F15" s="15" t="inlineStr">
         <is>
           <t>Row 15 negative; recipient filter</t>
         </is>
       </c>
-      <c r="F15" s="15" t="inlineStr">
+      <c r="G15" s="15" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1864,20 +1925,25 @@
       </c>
       <c r="C16" s="16" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Vacation.xlsx</t>
+        </is>
+      </c>
+      <c r="D16" s="16" t="inlineStr">
+        <is>
           <t>TS-Vac-Cron-AutoPay</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="E16" s="16" t="inlineStr">
         <is>
           <t>Auto-pay — vacations with payment_date in past and status APPROVED transition to PAID</t>
         </is>
       </c>
-      <c r="E16" s="16" t="inlineStr">
+      <c r="F16" s="16" t="inlineStr">
         <is>
           <t>Row 16 happy-path; baseline auto-pay scan</t>
         </is>
       </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="G16" s="16" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -1896,20 +1962,25 @@
       </c>
       <c r="C17" s="15" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Vacation.xlsx</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
           <t>TS-Vac-Cron-AutoPay</t>
         </is>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="E17" s="15" t="inlineStr">
         <is>
           <t>Auto-pay — vacations with payment_date in future are not transitioned</t>
         </is>
       </c>
-      <c r="E17" s="15" t="inlineStr">
+      <c r="F17" s="15" t="inlineStr">
         <is>
           <t>Row 16 negative; date-window filter</t>
         </is>
       </c>
-      <c r="F17" s="15" t="inlineStr">
+      <c r="G17" s="15" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -1928,20 +1999,25 @@
       </c>
       <c r="C18" s="16" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Vacation.xlsx</t>
+        </is>
+      </c>
+      <c r="D18" s="16" t="inlineStr">
+        <is>
           <t>TS-Vac-Cron-AutoPay</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="E18" s="16" t="inlineStr">
         <is>
           <t>Auto-pay — idempotent on repeated trigger within same day</t>
         </is>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="F18" s="16" t="inlineStr">
         <is>
           <t>Row 16 idempotency</t>
         </is>
       </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="G18" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -1960,20 +2036,25 @@
       </c>
       <c r="C19" s="15" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Vacation.xlsx</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
           <t>TS-Vac-Cron-ApprovedToPaid</t>
         </is>
       </c>
-      <c r="D19" s="15" t="inlineStr">
+      <c r="E19" s="15" t="inlineStr">
         <is>
           <t>Pay expired approved vacations — APPROVED vacations past payment_date transition to PAID</t>
         </is>
       </c>
-      <c r="E19" s="15" t="inlineStr">
+      <c r="F19" s="15" t="inlineStr">
         <is>
           <t>Row 17 happy-path; DB-only assertion (no SchedulerLock, no markers)</t>
         </is>
       </c>
-      <c r="F19" s="15" t="inlineStr">
+      <c r="G19" s="15" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -1992,20 +2073,25 @@
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Vacation.xlsx</t>
+        </is>
+      </c>
+      <c r="D20" s="16" t="inlineStr">
+        <is>
           <t>TS-Vac-Cron-ApprovedToPaid</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="E20" s="16" t="inlineStr">
         <is>
           <t>Pay expired approved — only expired APPROVED (payment_date ≤ today) are transitioned</t>
         </is>
       </c>
-      <c r="E20" s="16" t="inlineStr">
+      <c r="F20" s="16" t="inlineStr">
         <is>
           <t>Row 17 filter; ensures date-window logic</t>
         </is>
       </c>
-      <c r="F20" s="16" t="inlineStr">
+      <c r="G20" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2024,20 +2110,25 @@
       </c>
       <c r="C21" s="15" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Vacation.xlsx</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
           <t>TS-Vac-Cron-ApprovedToPaid</t>
         </is>
       </c>
-      <c r="D21" s="15" t="inlineStr">
+      <c r="E21" s="15" t="inlineStr">
         <is>
           <t>Pay expired approved — REJECTED / CANCELED / NEW vacations untouched</t>
         </is>
       </c>
-      <c r="E21" s="15" t="inlineStr">
+      <c r="F21" s="15" t="inlineStr">
         <is>
           <t>Row 17 status-filter negative</t>
         </is>
       </c>
-      <c r="F21" s="15" t="inlineStr">
+      <c r="G21" s="15" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2056,20 +2147,25 @@
       </c>
       <c r="C22" s="16" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Vacation.xlsx</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="inlineStr">
+        <is>
           <t>TS-Vac-Cron-EmpProjectSync</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="E22" s="16" t="inlineStr">
         <is>
           <t>Periodic employee-project sync — TTT→Vacation table mirrors employee_project_assignments</t>
         </is>
       </c>
-      <c r="E22" s="16" t="inlineStr">
+      <c r="F22" s="16" t="inlineStr">
         <is>
           <t>Row 18 happy-path</t>
         </is>
       </c>
-      <c r="F22" s="16" t="inlineStr">
+      <c r="G22" s="16" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -2088,20 +2184,25 @@
       </c>
       <c r="C23" s="15" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Vacation.xlsx</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="inlineStr">
+        <is>
           <t>TS-Vac-Cron-EmpProjectSync</t>
         </is>
       </c>
-      <c r="D23" s="15" t="inlineStr">
+      <c r="E23" s="15" t="inlineStr">
         <is>
           <t>Periodic employee-project sync — new assignment within window is propagated</t>
         </is>
       </c>
-      <c r="E23" s="15" t="inlineStr">
+      <c r="F23" s="15" t="inlineStr">
         <is>
           <t>Row 18 delta-detect</t>
         </is>
       </c>
-      <c r="F23" s="15" t="inlineStr">
+      <c r="G23" s="15" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2120,20 +2221,25 @@
       </c>
       <c r="C24" s="16" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Vacation.xlsx</t>
+        </is>
+      </c>
+      <c r="D24" s="16" t="inlineStr">
+        <is>
           <t>TS-Vac-Cron-EmpProjectSync</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="E24" s="16" t="inlineStr">
         <is>
           <t>Periodic employee-project sync — removed assignment within window is propagated</t>
         </is>
       </c>
-      <c r="E24" s="16" t="inlineStr">
+      <c r="F24" s="16" t="inlineStr">
         <is>
           <t>Row 18 delete-detect</t>
         </is>
       </c>
-      <c r="F24" s="16" t="inlineStr">
+      <c r="G24" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2152,20 +2258,25 @@
       </c>
       <c r="C25" s="15" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Vacation.xlsx</t>
+        </is>
+      </c>
+      <c r="D25" s="15" t="inlineStr">
+        <is>
           <t>TS-Vac-Cron-EmpProjectSync</t>
         </is>
       </c>
-      <c r="D25" s="15" t="inlineStr">
+      <c r="E25" s="15" t="inlineStr">
         <is>
           <t>Periodic employee-project sync — data-loss in sync window (WON'T FIX) reproduces and documents risk</t>
         </is>
       </c>
-      <c r="E25" s="15" t="inlineStr">
+      <c r="F25" s="15" t="inlineStr">
         <is>
           <t>Row 18 known risk; regression guard for documented WON'T FIX bug</t>
         </is>
       </c>
-      <c r="F25" s="15" t="inlineStr">
+      <c r="G25" s="15" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2184,20 +2295,25 @@
       </c>
       <c r="C26" s="16" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Vacation.xlsx</t>
+        </is>
+      </c>
+      <c r="D26" s="16" t="inlineStr">
+        <is>
           <t>TS-Vac-Cron-EmpProjectSync</t>
         </is>
       </c>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="E26" s="16" t="inlineStr">
         <is>
           <t>Periodic employee-project sync — idempotent on repeated trigger</t>
         </is>
       </c>
-      <c r="E26" s="16" t="inlineStr">
+      <c r="F26" s="16" t="inlineStr">
         <is>
           <t>Row 18 idempotency</t>
         </is>
       </c>
-      <c r="F26" s="16" t="inlineStr">
+      <c r="G26" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2216,20 +2332,25 @@
       </c>
       <c r="C27" s="15" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Vacation.xlsx</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="inlineStr">
+        <is>
           <t>TS-Vac-Cron-EmpProjectSync</t>
         </is>
       </c>
-      <c r="D27" s="15" t="inlineStr">
+      <c r="E27" s="15" t="inlineStr">
         <is>
           <t>Startup employee-project sync — runs on first boot after EMPLOYEE_PROJECT_INITIAL_SYNC marker absent</t>
         </is>
       </c>
-      <c r="E27" s="15" t="inlineStr">
+      <c r="F27" s="15" t="inlineStr">
         <is>
           <t>Row 19 startup happy-path; feature-toggle gated</t>
         </is>
       </c>
-      <c r="F27" s="15" t="inlineStr">
+      <c r="G27" s="15" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -2248,20 +2369,25 @@
       </c>
       <c r="C28" s="16" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Vacation.xlsx</t>
+        </is>
+      </c>
+      <c r="D28" s="16" t="inlineStr">
+        <is>
           <t>TS-Vac-Cron-EmpProjectSync</t>
         </is>
       </c>
-      <c r="D28" s="16" t="inlineStr">
+      <c r="E28" s="16" t="inlineStr">
         <is>
           <t>Startup employee-project sync — does not rerun when java_migration marker present</t>
         </is>
       </c>
-      <c r="E28" s="16" t="inlineStr">
+      <c r="F28" s="16" t="inlineStr">
         <is>
           <t>Row 19 idempotency gating</t>
         </is>
       </c>
-      <c r="F28" s="16" t="inlineStr">
+      <c r="G28" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2280,20 +2406,25 @@
       </c>
       <c r="C29" s="15" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Vacation.xlsx</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="inlineStr">
+        <is>
           <t>TS-Vac-Cron-EmpProjectSync</t>
         </is>
       </c>
-      <c r="D29" s="15" t="inlineStr">
+      <c r="E29" s="15" t="inlineStr">
         <is>
           <t>Startup employee-project sync — populates marker on successful completion</t>
         </is>
       </c>
-      <c r="E29" s="15" t="inlineStr">
+      <c r="F29" s="15" t="inlineStr">
         <is>
           <t>Row 19 marker-writes confirmation</t>
         </is>
       </c>
-      <c r="F29" s="15" t="inlineStr">
+      <c r="G29" s="15" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2312,20 +2443,25 @@
       </c>
       <c r="C30" s="16" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Vacation.xlsx</t>
+        </is>
+      </c>
+      <c r="D30" s="16" t="inlineStr">
+        <is>
           <t>TS-Vac-Cron-StatReportInit</t>
         </is>
       </c>
-      <c r="D30" s="16" t="inlineStr">
+      <c r="E30" s="16" t="inlineStr">
         <is>
           <t>Startup statistic-report sync — runs on first boot after STATISTIC_REPORT_INITIAL_SYNC marker absent</t>
         </is>
       </c>
-      <c r="E30" s="16" t="inlineStr">
+      <c r="F30" s="16" t="inlineStr">
         <is>
           <t>Row 21 startup happy-path; feature-toggle gated</t>
         </is>
       </c>
-      <c r="F30" s="16" t="inlineStr">
+      <c r="G30" s="16" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -2344,20 +2480,25 @@
       </c>
       <c r="C31" s="15" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Vacation.xlsx</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="inlineStr">
+        <is>
           <t>TS-Vac-Cron-StatReportInit</t>
         </is>
       </c>
-      <c r="D31" s="15" t="inlineStr">
+      <c r="E31" s="15" t="inlineStr">
         <is>
           <t>Startup statistic-report sync — does not rerun when java_migration marker present</t>
         </is>
       </c>
-      <c r="E31" s="15" t="inlineStr">
+      <c r="F31" s="15" t="inlineStr">
         <is>
           <t>Row 21 idempotency gating</t>
         </is>
       </c>
-      <c r="F31" s="15" t="inlineStr">
+      <c r="G31" s="15" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2376,20 +2517,25 @@
       </c>
       <c r="C32" s="16" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Reports.xlsx</t>
+        </is>
+      </c>
+      <c r="D32" s="16" t="inlineStr">
+        <is>
           <t>TS-Reports-CronNotifications</t>
         </is>
       </c>
-      <c r="D32" s="16" t="inlineStr">
+      <c r="E32" s="16" t="inlineStr">
         <is>
           <t>Forgotten-report reminder — employees with missing prior-day reports receive FORGOTTEN_REPORT email</t>
         </is>
       </c>
-      <c r="E32" s="16" t="inlineStr">
+      <c r="F32" s="16" t="inlineStr">
         <is>
           <t>Row 1 happy-path; baseline daily notification</t>
         </is>
       </c>
-      <c r="F32" s="16" t="inlineStr">
+      <c r="G32" s="16" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -2408,20 +2554,25 @@
       </c>
       <c r="C33" s="15" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Reports.xlsx</t>
+        </is>
+      </c>
+      <c r="D33" s="15" t="inlineStr">
+        <is>
           <t>TS-Reports-CronNotifications</t>
         </is>
       </c>
-      <c r="D33" s="15" t="inlineStr">
+      <c r="E33" s="15" t="inlineStr">
         <is>
           <t>Forgotten-report reminder — employees with fully-reported prior day not notified</t>
         </is>
       </c>
-      <c r="E33" s="15" t="inlineStr">
+      <c r="F33" s="15" t="inlineStr">
         <is>
           <t>Row 1 filter; missing-reports-only recipients</t>
         </is>
       </c>
-      <c r="F33" s="15" t="inlineStr">
+      <c r="G33" s="15" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2440,20 +2591,25 @@
       </c>
       <c r="C34" s="16" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Reports.xlsx</t>
+        </is>
+      </c>
+      <c r="D34" s="16" t="inlineStr">
+        <is>
           <t>TS-Reports-CronNotifications</t>
         </is>
       </c>
-      <c r="D34" s="16" t="inlineStr">
+      <c r="E34" s="16" t="inlineStr">
         <is>
           <t>Forgotten-report reminder — idempotent on repeated trigger within same day</t>
         </is>
       </c>
-      <c r="E34" s="16" t="inlineStr">
+      <c r="F34" s="16" t="inlineStr">
         <is>
           <t>Row 1 idempotency; ShedLock window guard</t>
         </is>
       </c>
-      <c r="F34" s="16" t="inlineStr">
+      <c r="G34" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2472,20 +2628,25 @@
       </c>
       <c r="C35" s="15" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Reports.xlsx</t>
+        </is>
+      </c>
+      <c r="D35" s="15" t="inlineStr">
+        <is>
           <t>TS-Reports-CronNotifications</t>
         </is>
       </c>
-      <c r="D35" s="15" t="inlineStr">
+      <c r="E35" s="15" t="inlineStr">
         <is>
           <t>Delayed forgotten-report reminder — two-days-prior employees without reports escalated</t>
         </is>
       </c>
-      <c r="E35" s="15" t="inlineStr">
+      <c r="F35" s="15" t="inlineStr">
         <is>
           <t>Row 2 happy-path; next-day escalation</t>
         </is>
       </c>
-      <c r="F35" s="15" t="inlineStr">
+      <c r="G35" s="15" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -2504,20 +2665,25 @@
       </c>
       <c r="C36" s="16" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Reports.xlsx</t>
+        </is>
+      </c>
+      <c r="D36" s="16" t="inlineStr">
+        <is>
           <t>TS-Reports-CronNotifications</t>
         </is>
       </c>
-      <c r="D36" s="16" t="inlineStr">
+      <c r="E36" s="16" t="inlineStr">
         <is>
           <t>Delayed forgotten-report reminder — inactive employees excluded from recipient list</t>
         </is>
       </c>
-      <c r="E36" s="16" t="inlineStr">
+      <c r="F36" s="16" t="inlineStr">
         <is>
           <t>Row 2 negative; recipient filter</t>
         </is>
       </c>
-      <c r="F36" s="16" t="inlineStr">
+      <c r="G36" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2536,20 +2702,25 @@
       </c>
       <c r="C37" s="15" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Reports.xlsx</t>
+        </is>
+      </c>
+      <c r="D37" s="15" t="inlineStr">
+        <is>
           <t>TS-Reports-CronNotifications</t>
         </is>
       </c>
-      <c r="D37" s="15" t="inlineStr">
+      <c r="E37" s="15" t="inlineStr">
         <is>
           <t>Report-sheet-changed — employees with modified reports receive REPORT_SHEET_CHANGED email</t>
         </is>
       </c>
-      <c r="E37" s="15" t="inlineStr">
+      <c r="F37" s="15" t="inlineStr">
         <is>
           <t>Row 3 happy-path; delta #1 folded (template key REPORT_SHEET_CHANGED, not TASK_REPORT_CHANGED)</t>
         </is>
       </c>
-      <c r="F37" s="15" t="inlineStr">
+      <c r="G37" s="15" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -2568,20 +2739,25 @@
       </c>
       <c r="C38" s="16" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Reports.xlsx</t>
+        </is>
+      </c>
+      <c r="D38" s="16" t="inlineStr">
+        <is>
           <t>TS-Reports-CronNotifications</t>
         </is>
       </c>
-      <c r="D38" s="16" t="inlineStr">
+      <c r="E38" s="16" t="inlineStr">
         <is>
           <t>Report-sheet-changed — email subject matches REPORT_SHEET_CHANGED template per delta #1</t>
         </is>
       </c>
-      <c r="E38" s="16" t="inlineStr">
+      <c r="F38" s="16" t="inlineStr">
         <is>
           <t>Row 3 template verification per delta #1</t>
         </is>
       </c>
-      <c r="F38" s="16" t="inlineStr">
+      <c r="G38" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2600,20 +2776,25 @@
       </c>
       <c r="C39" s="15" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Reports.xlsx</t>
+        </is>
+      </c>
+      <c r="D39" s="15" t="inlineStr">
+        <is>
           <t>TS-Reports-CronNotifications</t>
         </is>
       </c>
-      <c r="D39" s="15" t="inlineStr">
+      <c r="E39" s="15" t="inlineStr">
         <is>
           <t>Report-sheet-changed — idempotent on repeated trigger within same window</t>
         </is>
       </c>
-      <c r="E39" s="15" t="inlineStr">
+      <c r="F39" s="15" t="inlineStr">
         <is>
           <t>Row 3 idempotency</t>
         </is>
       </c>
-      <c r="F39" s="15" t="inlineStr">
+      <c r="G39" s="15" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2632,20 +2813,25 @@
       </c>
       <c r="C40" s="16" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Reports.xlsx</t>
+        </is>
+      </c>
+      <c r="D40" s="16" t="inlineStr">
+        <is>
           <t>TS-Reports-CronNotifications</t>
         </is>
       </c>
-      <c r="D40" s="16" t="inlineStr">
+      <c r="E40" s="16" t="inlineStr">
         <is>
           <t>Report-rejection notification — rejected reports trigger APPROVE_REJECT email to employee</t>
         </is>
       </c>
-      <c r="E40" s="16" t="inlineStr">
+      <c r="F40" s="16" t="inlineStr">
         <is>
           <t>Row 4 happy-path; email-only verification per delta #2 (zero log markers)</t>
         </is>
       </c>
-      <c r="F40" s="16" t="inlineStr">
+      <c r="G40" s="16" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -2664,20 +2850,25 @@
       </c>
       <c r="C41" s="15" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Reports.xlsx</t>
+        </is>
+      </c>
+      <c r="D41" s="15" t="inlineStr">
+        <is>
           <t>TS-Reports-CronNotifications</t>
         </is>
       </c>
-      <c r="D41" s="15" t="inlineStr">
+      <c r="E41" s="15" t="inlineStr">
         <is>
           <t>Report-rejection notification — DEBOUNCE_INTERVAL_MINUTES=5 suppresses repeat emails within window</t>
         </is>
       </c>
-      <c r="E41" s="15" t="inlineStr">
+      <c r="F41" s="15" t="inlineStr">
         <is>
           <t>Row 4 debounce guard; timing-sensitive</t>
         </is>
       </c>
-      <c r="F41" s="15" t="inlineStr">
+      <c r="G41" s="15" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2696,20 +2887,25 @@
       </c>
       <c r="C42" s="16" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Reports.xlsx</t>
+        </is>
+      </c>
+      <c r="D42" s="16" t="inlineStr">
+        <is>
           <t>TS-Reports-CronNotifications</t>
         </is>
       </c>
-      <c r="D42" s="16" t="inlineStr">
+      <c r="E42" s="16" t="inlineStr">
         <is>
           <t>Report-rejection notification — closed report month + open confirmation period still dispatches reject email (#3321)</t>
         </is>
       </c>
-      <c r="E42" s="16" t="inlineStr">
+      <c r="F42" s="16" t="inlineStr">
         <is>
           <t>Row 4 regression; #3321 folded</t>
         </is>
       </c>
-      <c r="F42" s="16" t="inlineStr">
+      <c r="G42" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2728,20 +2924,25 @@
       </c>
       <c r="C43" s="15" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Reports.xlsx</t>
+        </is>
+      </c>
+      <c r="D43" s="15" t="inlineStr">
+        <is>
           <t>TS-Reports-CronNotifications</t>
         </is>
       </c>
-      <c r="D43" s="15" t="inlineStr">
+      <c r="E43" s="15" t="inlineStr">
         <is>
           <t>Report-rejection notification — officeId=9 employees excluded per #685</t>
         </is>
       </c>
-      <c r="E43" s="15" t="inlineStr">
+      <c r="F43" s="15" t="inlineStr">
         <is>
           <t>Row 4 negative; office-filter per #685</t>
         </is>
       </c>
-      <c r="F43" s="15" t="inlineStr">
+      <c r="G43" s="15" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2760,20 +2961,25 @@
       </c>
       <c r="C44" s="16" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Reports.xlsx</t>
+        </is>
+      </c>
+      <c r="D44" s="16" t="inlineStr">
+        <is>
           <t>TS-Reports-CronNotifications</t>
         </is>
       </c>
-      <c r="D44" s="16" t="inlineStr">
+      <c r="E44" s="16" t="inlineStr">
         <is>
           <t>Cleanup-extended-period — expired extended-period approvals cleared for non-accountant employees</t>
         </is>
       </c>
-      <c r="E44" s="16" t="inlineStr">
+      <c r="F44" s="16" t="inlineStr">
         <is>
           <t>Row 7 happy-path; accountant-exclusion folded per #2289</t>
         </is>
       </c>
-      <c r="F44" s="16" t="inlineStr">
+      <c r="G44" s="16" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -2792,20 +2998,25 @@
       </c>
       <c r="C45" s="15" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Reports.xlsx</t>
+        </is>
+      </c>
+      <c r="D45" s="15" t="inlineStr">
+        <is>
           <t>TS-Reports-CronNotifications</t>
         </is>
       </c>
-      <c r="D45" s="15" t="inlineStr">
+      <c r="E45" s="15" t="inlineStr">
         <is>
           <t>Cleanup-extended-period — accountant-role employees not cleaned up per #2289</t>
         </is>
       </c>
-      <c r="E45" s="15" t="inlineStr">
+      <c r="F45" s="15" t="inlineStr">
         <is>
           <t>Row 7 negative; accountant-exclusion regression per #2289</t>
         </is>
       </c>
-      <c r="F45" s="15" t="inlineStr">
+      <c r="G45" s="15" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2824,20 +3035,25 @@
       </c>
       <c r="C46" s="16" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Reports.xlsx</t>
+        </is>
+      </c>
+      <c r="D46" s="16" t="inlineStr">
+        <is>
           <t>TS-Reports-CronNotifications</t>
         </is>
       </c>
-      <c r="D46" s="16" t="inlineStr">
+      <c r="E46" s="16" t="inlineStr">
         <is>
           <t>Cleanup-extended-period — idempotent on repeated trigger within same day</t>
         </is>
       </c>
-      <c r="E46" s="16" t="inlineStr">
+      <c r="F46" s="16" t="inlineStr">
         <is>
           <t>Row 7 idempotency</t>
         </is>
       </c>
-      <c r="F46" s="16" t="inlineStr">
+      <c r="G46" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -2856,20 +3072,25 @@
       </c>
       <c r="C47" s="15" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Reports.xlsx</t>
+        </is>
+      </c>
+      <c r="D47" s="15" t="inlineStr">
+        <is>
           <t>TS-Reports-BudgetNotifications</t>
         </is>
       </c>
-      <c r="D47" s="15" t="inlineStr">
+      <c r="E47" s="15" t="inlineStr">
         <is>
           <t>Budget-notification — BUDGET_NOTIFICATION_EXCEEDED dispatched when project budget crossed above threshold</t>
         </is>
       </c>
-      <c r="E47" s="15" t="inlineStr">
+      <c r="F47" s="15" t="inlineStr">
         <is>
           <t>Row 5 EXCEEDED path; delta #3 folded (3 templates, not 1)</t>
         </is>
       </c>
-      <c r="F47" s="15" t="inlineStr">
+      <c r="G47" s="15" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -2888,20 +3109,25 @@
       </c>
       <c r="C48" s="16" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Reports.xlsx</t>
+        </is>
+      </c>
+      <c r="D48" s="16" t="inlineStr">
+        <is>
           <t>TS-Reports-BudgetNotifications</t>
         </is>
       </c>
-      <c r="D48" s="16" t="inlineStr">
+      <c r="E48" s="16" t="inlineStr">
         <is>
           <t>Budget-notification — BUDGET_NOTIFICATION_NOT_REACHED dispatched when budget not met by deadline</t>
         </is>
       </c>
-      <c r="E48" s="16" t="inlineStr">
+      <c r="F48" s="16" t="inlineStr">
         <is>
           <t>Row 5 NOT_REACHED path; delta #3</t>
         </is>
       </c>
-      <c r="F48" s="16" t="inlineStr">
+      <c r="G48" s="16" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -2920,20 +3146,25 @@
       </c>
       <c r="C49" s="15" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Reports.xlsx</t>
+        </is>
+      </c>
+      <c r="D49" s="15" t="inlineStr">
+        <is>
           <t>TS-Reports-BudgetNotifications</t>
         </is>
       </c>
-      <c r="D49" s="15" t="inlineStr">
+      <c r="E49" s="15" t="inlineStr">
         <is>
           <t>Budget-notification — BUDGET_NOTIFICATION_DATE_UPDATED dispatched when budget deadline moved</t>
         </is>
       </c>
-      <c r="E49" s="15" t="inlineStr">
+      <c r="F49" s="15" t="inlineStr">
         <is>
           <t>Row 5 DATE_UPDATED path; delta #3</t>
         </is>
       </c>
-      <c r="F49" s="15" t="inlineStr">
+      <c r="G49" s="15" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2952,20 +3183,25 @@
       </c>
       <c r="C50" s="16" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Reports.xlsx</t>
+        </is>
+      </c>
+      <c r="D50" s="16" t="inlineStr">
+        <is>
           <t>TS-Reports-BudgetNotifications</t>
         </is>
       </c>
-      <c r="D50" s="16" t="inlineStr">
+      <c r="E50" s="16" t="inlineStr">
         <is>
           <t>Budget-notification — SAFETY_INTERVAL_SECONDS=10 suppresses rapid-fire dispatch</t>
         </is>
       </c>
-      <c r="E50" s="16" t="inlineStr">
+      <c r="F50" s="16" t="inlineStr">
         <is>
           <t>Row 5 safety-interval guard per #892</t>
         </is>
       </c>
-      <c r="F50" s="16" t="inlineStr">
+      <c r="G50" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -2984,20 +3220,25 @@
       </c>
       <c r="C51" s="15" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Reports.xlsx</t>
+        </is>
+      </c>
+      <c r="D51" s="15" t="inlineStr">
+        <is>
           <t>TS-Reports-BudgetNotifications</t>
         </is>
       </c>
-      <c r="D51" s="15" t="inlineStr">
+      <c r="E51" s="15" t="inlineStr">
         <is>
           <t>Budget-notification — idempotent on repeated trigger within same window</t>
         </is>
       </c>
-      <c r="E51" s="15" t="inlineStr">
+      <c r="F51" s="15" t="inlineStr">
         <is>
           <t>Row 5 idempotency</t>
         </is>
       </c>
-      <c r="F51" s="15" t="inlineStr">
+      <c r="G51" s="15" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3016,20 +3257,25 @@
       </c>
       <c r="C52" s="16" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_CrossService.xlsx</t>
+        </is>
+      </c>
+      <c r="D52" s="16" t="inlineStr">
+        <is>
           <t>TS-CrossService-CronCSSync</t>
         </is>
       </c>
-      <c r="D52" s="16" t="inlineStr">
+      <c r="E52" s="16" t="inlineStr">
         <is>
           <t>CS sync (ttt) — cron fires every 15 min and emits started/finished markers</t>
         </is>
       </c>
-      <c r="E52" s="16" t="inlineStr">
+      <c r="F52" s="16" t="inlineStr">
         <is>
           <t>Row 6 happy-path; baseline partial sync</t>
         </is>
       </c>
-      <c r="F52" s="16" t="inlineStr">
+      <c r="G52" s="16" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -3048,20 +3294,25 @@
       </c>
       <c r="C53" s="15" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_CrossService.xlsx</t>
+        </is>
+      </c>
+      <c r="D53" s="15" t="inlineStr">
+        <is>
           <t>TS-CrossService-CronCSSync</t>
         </is>
       </c>
-      <c r="D53" s="15" t="inlineStr">
+      <c r="E53" s="15" t="inlineStr">
         <is>
           <t>CS sync (ttt) — Unleash flag CS_SYNC-qa-1 OFF makes launcher skip silently</t>
         </is>
       </c>
-      <c r="E53" s="15" t="inlineStr">
+      <c r="F53" s="15" t="inlineStr">
         <is>
           <t>Row 6 negative; feature-toggle gated silence</t>
         </is>
       </c>
-      <c r="F53" s="15" t="inlineStr">
+      <c r="G53" s="15" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -3080,20 +3331,25 @@
       </c>
       <c r="C54" s="16" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_CrossService.xlsx</t>
+        </is>
+      </c>
+      <c r="D54" s="16" t="inlineStr">
+        <is>
           <t>TS-CrossService-CronCSSync</t>
         </is>
       </c>
-      <c r="D54" s="16" t="inlineStr">
+      <c r="E54" s="16" t="inlineStr">
         <is>
           <t>CS sync (ttt) — full sync fires at application startup only (no cron path)</t>
         </is>
       </c>
-      <c r="E54" s="16" t="inlineStr">
+      <c r="F54" s="16" t="inlineStr">
         <is>
           <t>Row 6 startup-only full sync; delta #10 folded</t>
         </is>
       </c>
-      <c r="F54" s="16" t="inlineStr">
+      <c r="G54" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -3112,20 +3368,25 @@
       </c>
       <c r="C55" s="15" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_CrossService.xlsx</t>
+        </is>
+      </c>
+      <c r="D55" s="15" t="inlineStr">
+        <is>
           <t>TS-CrossService-CronCSSync</t>
         </is>
       </c>
-      <c r="D55" s="15" t="inlineStr">
+      <c r="E55" s="15" t="inlineStr">
         <is>
           <t>CS sync (vacation) — cron fires and emits distinct `CS sync started/finished` markers</t>
         </is>
       </c>
-      <c r="E55" s="15" t="inlineStr">
+      <c r="F55" s="15" t="inlineStr">
         <is>
           <t>Row 10 happy-path; design asymmetry (different marker text vs rows 6/20)</t>
         </is>
       </c>
-      <c r="F55" s="15" t="inlineStr">
+      <c r="G55" s="15" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -3144,20 +3405,25 @@
       </c>
       <c r="C56" s="16" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_CrossService.xlsx</t>
+        </is>
+      </c>
+      <c r="D56" s="16" t="inlineStr">
+        <is>
           <t>TS-CrossService-CronCSSync</t>
         </is>
       </c>
-      <c r="D56" s="16" t="inlineStr">
+      <c r="E56" s="16" t="inlineStr">
         <is>
           <t>CS sync (vacation) — failure path logs at WARN level (not ERROR)</t>
         </is>
       </c>
-      <c r="E56" s="16" t="inlineStr">
+      <c r="F56" s="16" t="inlineStr">
         <is>
           <t>Row 10 design issue; WARN-level regression guard</t>
         </is>
       </c>
-      <c r="F56" s="16" t="inlineStr">
+      <c r="G56" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3176,20 +3442,25 @@
       </c>
       <c r="C57" s="15" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_CrossService.xlsx</t>
+        </is>
+      </c>
+      <c r="D57" s="15" t="inlineStr">
+        <is>
           <t>TS-CrossService-CronCSSync</t>
         </is>
       </c>
-      <c r="D57" s="15" t="inlineStr">
+      <c r="E57" s="15" t="inlineStr">
         <is>
           <t>CS sync (calendar) — fullSync=false via v2 test endpoint runs partial sync</t>
         </is>
       </c>
-      <c r="E57" s="15" t="inlineStr">
+      <c r="F57" s="15" t="inlineStr">
         <is>
           <t>Row 20 happy-path partial; delta #7 endpoint folded</t>
         </is>
       </c>
-      <c r="F57" s="15" t="inlineStr">
+      <c r="G57" s="15" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -3208,20 +3479,25 @@
       </c>
       <c r="C58" s="16" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_CrossService.xlsx</t>
+        </is>
+      </c>
+      <c r="D58" s="16" t="inlineStr">
+        <is>
           <t>TS-CrossService-CronCSSync</t>
         </is>
       </c>
-      <c r="D58" s="16" t="inlineStr">
+      <c r="E58" s="16" t="inlineStr">
         <is>
           <t>CS sync (calendar) — fullSync=true via v2 test endpoint runs full sync</t>
         </is>
       </c>
-      <c r="E58" s="16" t="inlineStr">
+      <c r="F58" s="16" t="inlineStr">
         <is>
           <t>Row 20 full sync via v2 endpoint; delta #7</t>
         </is>
       </c>
-      <c r="F58" s="16" t="inlineStr">
+      <c r="G58" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -3240,20 +3516,25 @@
       </c>
       <c r="C59" s="15" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_CrossService.xlsx</t>
+        </is>
+      </c>
+      <c r="D59" s="15" t="inlineStr">
+        <is>
           <t>TS-CrossService-CronCSSync</t>
         </is>
       </c>
-      <c r="D59" s="15" t="inlineStr">
+      <c r="E59" s="15" t="inlineStr">
         <is>
           <t>CS sync — marker collision: rows 6 and 20 both emit same text (disambiguate by stream)</t>
         </is>
       </c>
-      <c r="E59" s="15" t="inlineStr">
+      <c r="F59" s="15" t="inlineStr">
         <is>
           <t>Shared rows 6+20; Graylog stream field disambiguation</t>
         </is>
       </c>
-      <c r="F59" s="15" t="inlineStr">
+      <c r="G59" s="15" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -3272,20 +3553,25 @@
       </c>
       <c r="C60" s="16" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_CrossService.xlsx</t>
+        </is>
+      </c>
+      <c r="D60" s="16" t="inlineStr">
+        <is>
           <t>TS-CrossService-CronCSSync</t>
         </is>
       </c>
-      <c r="D60" s="16" t="inlineStr">
+      <c r="E60" s="16" t="inlineStr">
         <is>
           <t>CS sync — ShedLock: concurrent pods do not double-execute within lock window</t>
         </is>
       </c>
-      <c r="E60" s="16" t="inlineStr">
+      <c r="F60" s="16" t="inlineStr">
         <is>
           <t>Shared rows 6/10/20; ShedLock distributed-lock guard</t>
         </is>
       </c>
-      <c r="F60" s="16" t="inlineStr">
+      <c r="G60" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -3304,20 +3590,25 @@
       </c>
       <c r="C61" s="15" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_CrossService.xlsx</t>
+        </is>
+      </c>
+      <c r="D61" s="15" t="inlineStr">
+        <is>
           <t>TS-CrossService-CronCSSync</t>
         </is>
       </c>
-      <c r="D61" s="15" t="inlineStr">
+      <c r="E61" s="15" t="inlineStr">
         <is>
           <t>CS sync — parallel execution across services: ttt + vacation + calendar run concurrently</t>
         </is>
       </c>
-      <c r="E61" s="15" t="inlineStr">
+      <c r="F61" s="15" t="inlineStr">
         <is>
           <t>Shared rows 6/10/20; per-service independence</t>
         </is>
       </c>
-      <c r="F61" s="15" t="inlineStr">
+      <c r="G61" s="15" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3336,20 +3627,25 @@
       </c>
       <c r="C62" s="16" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_CrossService.xlsx</t>
+        </is>
+      </c>
+      <c r="D62" s="16" t="inlineStr">
+        <is>
           <t>TS-CrossService-CronCSSync</t>
         </is>
       </c>
-      <c r="D62" s="16" t="inlineStr">
+      <c r="E62" s="16" t="inlineStr">
         <is>
           <t>CS sync — idempotency: re-trigger within lock window has no effect</t>
         </is>
       </c>
-      <c r="E62" s="16" t="inlineStr">
+      <c r="F62" s="16" t="inlineStr">
         <is>
           <t>Shared rows 6/10/20 idempotency</t>
         </is>
       </c>
-      <c r="F62" s="16" t="inlineStr">
+      <c r="G62" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3368,20 +3664,25 @@
       </c>
       <c r="C63" s="15" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_CrossService.xlsx</t>
+        </is>
+      </c>
+      <c r="D63" s="15" t="inlineStr">
+        <is>
           <t>TS-CrossService-CronPMToolSync</t>
         </is>
       </c>
-      <c r="D63" s="15" t="inlineStr">
+      <c r="E63" s="15" t="inlineStr">
         <is>
           <t>PM Tool sync — new project in PMT propagates to TTT with all synced fields</t>
         </is>
       </c>
-      <c r="E63" s="15" t="inlineStr">
+      <c r="F63" s="15" t="inlineStr">
         <is>
           <t>Row 23 happy-path; #3083 contract baseline</t>
         </is>
       </c>
-      <c r="F63" s="15" t="inlineStr">
+      <c r="G63" s="15" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -3400,20 +3701,25 @@
       </c>
       <c r="C64" s="16" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_CrossService.xlsx</t>
+        </is>
+      </c>
+      <c r="D64" s="16" t="inlineStr">
+        <is>
           <t>TS-CrossService-CronPMToolSync</t>
         </is>
       </c>
-      <c r="D64" s="16" t="inlineStr">
+      <c r="E64" s="16" t="inlineStr">
         <is>
           <t>PM Tool sync — existing project update: name/customer/status/supervisor fields mirrored</t>
         </is>
       </c>
-      <c r="E64" s="16" t="inlineStr">
+      <c r="F64" s="16" t="inlineStr">
         <is>
           <t>Row 23 update flow; #3083 field contract</t>
         </is>
       </c>
-      <c r="F64" s="16" t="inlineStr">
+      <c r="G64" s="16" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -3432,20 +3738,25 @@
       </c>
       <c r="C65" s="15" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_CrossService.xlsx</t>
+        </is>
+      </c>
+      <c r="D65" s="15" t="inlineStr">
+        <is>
           <t>TS-CrossService-CronPMToolSync</t>
         </is>
       </c>
-      <c r="D65" s="15" t="inlineStr">
+      <c r="E65" s="15" t="inlineStr">
         <is>
           <t>PM Tool sync — presales merge is APPEND-ONLY (existing presales preserved)</t>
         </is>
       </c>
-      <c r="E65" s="15" t="inlineStr">
+      <c r="F65" s="15" t="inlineStr">
         <is>
           <t>Row 23 regression; #3382 append-only merge</t>
         </is>
       </c>
-      <c r="F65" s="15" t="inlineStr">
+      <c r="G65" s="15" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -3464,20 +3775,25 @@
       </c>
       <c r="C66" s="16" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_CrossService.xlsx</t>
+        </is>
+      </c>
+      <c r="D66" s="16" t="inlineStr">
+        <is>
           <t>TS-CrossService-CronPMToolSync</t>
         </is>
       </c>
-      <c r="D66" s="16" t="inlineStr">
+      <c r="E66" s="16" t="inlineStr">
         <is>
           <t>PM Tool sync — accounting_name is IMMUTABLE (PMT rename ignored)</t>
         </is>
       </c>
-      <c r="E66" s="16" t="inlineStr">
+      <c r="F66" s="16" t="inlineStr">
         <is>
           <t>Row 23 regression; #3286 accounting-name immutability</t>
         </is>
       </c>
-      <c r="F66" s="16" t="inlineStr">
+      <c r="G66" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -3496,20 +3812,25 @@
       </c>
       <c r="C67" s="15" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_CrossService.xlsx</t>
+        </is>
+      </c>
+      <c r="D67" s="15" t="inlineStr">
+        <is>
           <t>TS-CrossService-CronPMToolSync</t>
         </is>
       </c>
-      <c r="D67" s="15" t="inlineStr">
+      <c r="E67" s="15" t="inlineStr">
         <is>
           <t>PM Tool sync — default tracker-script auto-populated without history event</t>
         </is>
       </c>
-      <c r="E67" s="15" t="inlineStr">
+      <c r="F67" s="15" t="inlineStr">
         <is>
           <t>Row 23 regression; #3083 note on silent default populate</t>
         </is>
       </c>
-      <c r="F67" s="15" t="inlineStr">
+      <c r="G67" s="15" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -3528,20 +3849,25 @@
       </c>
       <c r="C68" s="16" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_CrossService.xlsx</t>
+        </is>
+      </c>
+      <c r="D68" s="16" t="inlineStr">
+        <is>
           <t>TS-CrossService-CronPMToolSync</t>
         </is>
       </c>
-      <c r="D68" s="16" t="inlineStr">
+      <c r="E68" s="16" t="inlineStr">
         <is>
           <t>PM Tool sync — PMT-owned field edits do NOT produce project_event rows</t>
         </is>
       </c>
-      <c r="E68" s="16" t="inlineStr">
+      <c r="F68" s="16" t="inlineStr">
         <is>
           <t>Row 23 event-history contract; PMT-owned silent writes</t>
         </is>
       </c>
-      <c r="F68" s="16" t="inlineStr">
+      <c r="G68" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -3560,20 +3886,25 @@
       </c>
       <c r="C69" s="15" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_CrossService.xlsx</t>
+        </is>
+      </c>
+      <c r="D69" s="15" t="inlineStr">
+        <is>
           <t>TS-CrossService-CronPMToolSync</t>
         </is>
       </c>
-      <c r="D69" s="15" t="inlineStr">
+      <c r="E69" s="15" t="inlineStr">
         <is>
           <t>TTT-owned field edit (tracker script) via UI produces project_event row (#3083 note 4)</t>
         </is>
       </c>
-      <c r="E69" s="15" t="inlineStr">
+      <c r="F69" s="15" t="inlineStr">
         <is>
           <t>Row 23 regression; snavrockiy fix 2026-02-25</t>
         </is>
       </c>
-      <c r="F69" s="15" t="inlineStr">
+      <c r="G69" s="15" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -3592,20 +3923,25 @@
       </c>
       <c r="C70" s="16" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_CrossService.xlsx</t>
+        </is>
+      </c>
+      <c r="D70" s="16" t="inlineStr">
+        <is>
           <t>TS-CrossService-CronPMToolSync</t>
         </is>
       </c>
-      <c r="D70" s="16" t="inlineStr">
+      <c r="E70" s="16" t="inlineStr">
         <is>
           <t>PM Tool sync — cs-id validation failure: unknown cs-id logged and skipped</t>
         </is>
       </c>
-      <c r="E70" s="16" t="inlineStr">
+      <c r="F70" s="16" t="inlineStr">
         <is>
           <t>Row 23 negative; cs-id FK guard</t>
         </is>
       </c>
-      <c r="F70" s="16" t="inlineStr">
+      <c r="G70" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -3624,20 +3960,25 @@
       </c>
       <c r="C71" s="15" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_CrossService.xlsx</t>
+        </is>
+      </c>
+      <c r="D71" s="15" t="inlineStr">
+        <is>
           <t>TS-CrossService-CronPMToolSync</t>
         </is>
       </c>
-      <c r="D71" s="15" t="inlineStr">
+      <c r="E71" s="15" t="inlineStr">
         <is>
           <t>PM Tool sync — Unleash `PM_TOOL_SYNC-qa-1` OFF: scheduler silent</t>
         </is>
       </c>
-      <c r="E71" s="15" t="inlineStr">
+      <c r="F71" s="15" t="inlineStr">
         <is>
           <t>Row 23 negative; feature-toggle gated silence</t>
         </is>
       </c>
-      <c r="F71" s="15" t="inlineStr">
+      <c r="G71" s="15" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -3656,20 +3997,25 @@
       </c>
       <c r="C72" s="16" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_CrossService.xlsx</t>
+        </is>
+      </c>
+      <c r="D72" s="16" t="inlineStr">
+        <is>
           <t>TS-CrossService-CronPMToolSync</t>
         </is>
       </c>
-      <c r="D72" s="16" t="inlineStr">
+      <c r="E72" s="16" t="inlineStr">
         <is>
           <t>PM Tool sync — startup full sync via TttStartupApplicationListener</t>
         </is>
       </c>
-      <c r="E72" s="16" t="inlineStr">
+      <c r="F72" s="16" t="inlineStr">
         <is>
           <t>Row 23 startup-only full sync; #3399 startup listener</t>
         </is>
       </c>
-      <c r="F72" s="16" t="inlineStr">
+      <c r="G72" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -3688,20 +4034,25 @@
       </c>
       <c r="C73" s="15" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Statistics.xlsx</t>
+        </is>
+      </c>
+      <c r="D73" s="15" t="inlineStr">
+        <is>
           <t>TS-Stat-CronStatReportSync</t>
         </is>
       </c>
-      <c r="D73" s="15" t="inlineStr">
+      <c r="E73" s="15" t="inlineStr">
         <is>
           <t>StatisticReportScheduler — cron fires at 04:00 NSK, ShedLock acquired/released, start/finish markers emit</t>
         </is>
       </c>
-      <c r="E73" s="15" t="inlineStr">
+      <c r="F73" s="15" t="inlineStr">
         <is>
           <t>Row 22 happy-path; baseline periodic sync with ShedLock</t>
         </is>
       </c>
-      <c r="F73" s="15" t="inlineStr">
+      <c r="G73" s="15" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -3720,20 +4071,25 @@
       </c>
       <c r="C74" s="16" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Statistics.xlsx</t>
+        </is>
+      </c>
+      <c r="D74" s="16" t="inlineStr">
+        <is>
           <t>TS-Stat-CronStatReportSync</t>
         </is>
       </c>
-      <c r="D74" s="16" t="inlineStr">
+      <c r="E74" s="16" t="inlineStr">
         <is>
           <t>Delta #8 regression — statistic-report sync failure logged at INFO (level:6), NOT ERROR (level:3)</t>
         </is>
       </c>
-      <c r="E74" s="16" t="inlineStr">
+      <c r="F74" s="16" t="inlineStr">
         <is>
           <t>Row 22 design issue; delta #8 log-level regression guard</t>
         </is>
       </c>
-      <c r="F74" s="16" t="inlineStr">
+      <c r="G74" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -3752,20 +4108,25 @@
       </c>
       <c r="C75" s="15" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Statistics.xlsx</t>
+        </is>
+      </c>
+      <c r="D75" s="15" t="inlineStr">
+        <is>
           <t>TS-Stat-CronStatReportSync</t>
         </is>
       </c>
-      <c r="D75" s="15" t="inlineStr">
+      <c r="E75" s="15" t="inlineStr">
         <is>
           <t>#3345 Bug 1 regression — employment-period filter excludes pre-hire and post-leave months</t>
         </is>
       </c>
-      <c r="E75" s="15" t="inlineStr">
+      <c r="F75" s="15" t="inlineStr">
         <is>
           <t>Row 22 regression; #3345 MR !5101 fix</t>
         </is>
       </c>
-      <c r="F75" s="15" t="inlineStr">
+      <c r="G75" s="15" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -3784,20 +4145,25 @@
       </c>
       <c r="C76" s="16" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Statistics.xlsx</t>
+        </is>
+      </c>
+      <c r="D76" s="16" t="inlineStr">
+        <is>
           <t>TS-Stat-CronStatReportSync</t>
         </is>
       </c>
-      <c r="D76" s="16" t="inlineStr">
+      <c r="E76" s="16" t="inlineStr">
         <is>
           <t>#3345 Bug 2 regression — day-off reschedule triggers month_norm recalc via RabbitMQ event</t>
         </is>
       </c>
-      <c r="E76" s="16" t="inlineStr">
+      <c r="F76" s="16" t="inlineStr">
         <is>
           <t>Row 22 regression; #3345 event-fan-out fix</t>
         </is>
       </c>
-      <c r="F76" s="16" t="inlineStr">
+      <c r="G76" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -3816,20 +4182,25 @@
       </c>
       <c r="C77" s="15" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Statistics.xlsx</t>
+        </is>
+      </c>
+      <c r="D77" s="15" t="inlineStr">
+        <is>
           <t>TS-Stat-CronStatReportSync</t>
         </is>
       </c>
-      <c r="D77" s="15" t="inlineStr">
+      <c r="E77" s="15" t="inlineStr">
         <is>
           <t>#3337 regression — sick-leave creation updates month_norm and reported_effort via SICK_LEAVE_CHANGES event</t>
         </is>
       </c>
-      <c r="E77" s="15" t="inlineStr">
+      <c r="F77" s="15" t="inlineStr">
         <is>
           <t>Row 22 regression; #3337 event-enum broadening</t>
         </is>
       </c>
-      <c r="F77" s="15" t="inlineStr">
+      <c r="G77" s="15" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -3848,20 +4219,25 @@
       </c>
       <c r="C78" s="16" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Statistics.xlsx</t>
+        </is>
+      </c>
+      <c r="D78" s="16" t="inlineStr">
+        <is>
           <t>TS-Stat-CronStatReportSync</t>
         </is>
       </c>
-      <c r="D78" s="16" t="inlineStr">
+      <c r="E78" s="16" t="inlineStr">
         <is>
           <t>#3337 regression — scoped event for employee A does NOT delete statistic_report rows for employee B</t>
         </is>
       </c>
-      <c r="E78" s="16" t="inlineStr">
+      <c r="F78" s="16" t="inlineStr">
         <is>
           <t>Row 22 regression; #3337 scoped-delete fix</t>
         </is>
       </c>
-      <c r="F78" s="16" t="inlineStr">
+      <c r="G78" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -3880,20 +4256,25 @@
       </c>
       <c r="C79" s="15" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Statistics.xlsx</t>
+        </is>
+      </c>
+      <c r="D79" s="15" t="inlineStr">
+        <is>
           <t>TS-Stat-CronStatReportSync</t>
         </is>
       </c>
-      <c r="D79" s="15" t="inlineStr">
+      <c r="E79" s="15" t="inlineStr">
         <is>
           <t>#3346 regression (bug #895498) — manual statistic_report row delete is restored on next optimized sync</t>
         </is>
       </c>
-      <c r="E79" s="15" t="inlineStr">
+      <c r="F79" s="15" t="inlineStr">
         <is>
           <t>Row 22 regression; #3346 scheduler-wiring fix</t>
         </is>
       </c>
-      <c r="F79" s="15" t="inlineStr">
+      <c r="G79" s="15" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -3912,20 +4293,25 @@
       </c>
       <c r="C80" s="16" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Statistics.xlsx</t>
+        </is>
+      </c>
+      <c r="D80" s="16" t="inlineStr">
+        <is>
           <t>TS-Stat-CronStatReportSync</t>
         </is>
       </c>
-      <c r="D80" s="16" t="inlineStr">
+      <c r="E80" s="16" t="inlineStr">
         <is>
           <t>Full vs optimized sync contract — full refreshes previous + current year; optimized refreshes previous + current month only</t>
         </is>
       </c>
-      <c r="E80" s="16" t="inlineStr">
+      <c r="F80" s="16" t="inlineStr">
         <is>
           <t>Row 22 endpoint-contract; #3345 note 894873</t>
         </is>
       </c>
-      <c r="F80" s="16" t="inlineStr">
+      <c r="G80" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -3944,20 +4330,25 @@
       </c>
       <c r="C81" s="15" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Email.xlsx</t>
+        </is>
+      </c>
+      <c r="D81" s="15" t="inlineStr">
+        <is>
           <t>TS-Email-CronDispatch</t>
         </is>
       </c>
-      <c r="D81" s="15" t="inlineStr">
+      <c r="E81" s="15" t="inlineStr">
         <is>
           <t>EmailSendScheduler — cron fires every 20 s, ShedLock acquired/released, start/finish markers emit</t>
         </is>
       </c>
-      <c r="E81" s="15" t="inlineStr">
+      <c r="F81" s="15" t="inlineStr">
         <is>
           <t>Row 8 happy-path; baseline dispatcher cadence + lock</t>
         </is>
       </c>
-      <c r="F81" s="15" t="inlineStr">
+      <c r="G81" s="15" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -3976,20 +4367,25 @@
       </c>
       <c r="C82" s="16" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Email.xlsx</t>
+        </is>
+      </c>
+      <c r="D82" s="16" t="inlineStr">
+        <is>
           <t>TS-Email-CronDispatch</t>
         </is>
       </c>
-      <c r="D82" s="16" t="inlineStr">
+      <c r="E82" s="16" t="inlineStr">
         <is>
           <t>Dispatch — NEW email transitions to SENT after SMTP success (happy path)</t>
         </is>
       </c>
-      <c r="E82" s="16" t="inlineStr">
+      <c r="F82" s="16" t="inlineStr">
         <is>
           <t>Row 8 SMTP-success status transition</t>
         </is>
       </c>
-      <c r="F82" s="16" t="inlineStr">
+      <c r="G82" s="16" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -4008,20 +4404,25 @@
       </c>
       <c r="C83" s="15" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Email.xlsx</t>
+        </is>
+      </c>
+      <c r="D83" s="15" t="inlineStr">
+        <is>
           <t>TS-Email-CronDispatch</t>
         </is>
       </c>
-      <c r="D83" s="15" t="inlineStr">
+      <c r="E83" s="15" t="inlineStr">
         <is>
           <t>Dispatch — invalid recipient transitions NEW → INVALID (SendFailedException path)</t>
         </is>
       </c>
-      <c r="E83" s="15" t="inlineStr">
+      <c r="F83" s="15" t="inlineStr">
         <is>
           <t>Row 8 invalid-recipient status transition</t>
         </is>
       </c>
-      <c r="F83" s="15" t="inlineStr">
+      <c r="G83" s="15" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -4040,20 +4441,25 @@
       </c>
       <c r="C84" s="16" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Email.xlsx</t>
+        </is>
+      </c>
+      <c r="D84" s="16" t="inlineStr">
+        <is>
           <t>TS-Email-CronDispatch</t>
         </is>
       </c>
-      <c r="D84" s="16" t="inlineStr">
+      <c r="E84" s="16" t="inlineStr">
         <is>
           <t>Dispatch — partial SMTP failure sets FAILED for rejected messages, SENT for accepted</t>
         </is>
       </c>
-      <c r="E84" s="16" t="inlineStr">
+      <c r="F84" s="16" t="inlineStr">
         <is>
           <t>Row 8 mixed-batch status transitions; DI-EMAIL-DISPATCH-RETRY context</t>
         </is>
       </c>
-      <c r="F84" s="16" t="inlineStr">
+      <c r="G84" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -4072,20 +4478,25 @@
       </c>
       <c r="C85" s="15" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Email.xlsx</t>
+        </is>
+      </c>
+      <c r="D85" s="15" t="inlineStr">
+        <is>
           <t>TS-Email-CronDispatch</t>
         </is>
       </c>
-      <c r="D85" s="15" t="inlineStr">
+      <c r="E85" s="15" t="inlineStr">
         <is>
           <t>DI-EMAIL-DISPATCH-AUTH regression — MailAuthenticationException caught, status NOT updated, infinite retry loop</t>
         </is>
       </c>
-      <c r="E85" s="15" t="inlineStr">
+      <c r="F85" s="15" t="inlineStr">
         <is>
           <t>Row 8 design-issue regression guard; stuck-as-NEW infinite loop</t>
         </is>
       </c>
-      <c r="F85" s="15" t="inlineStr">
+      <c r="G85" s="15" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -4104,20 +4515,25 @@
       </c>
       <c r="C86" s="16" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Email.xlsx</t>
+        </is>
+      </c>
+      <c r="D86" s="16" t="inlineStr">
+        <is>
           <t>TS-Email-CronDispatch</t>
         </is>
       </c>
-      <c r="D86" s="16" t="inlineStr">
+      <c r="E86" s="16" t="inlineStr">
         <is>
           <t>Dispatch — pageSize = 300 caps per-batch dispatch; overflow drains in subsequent ticks</t>
         </is>
       </c>
-      <c r="E86" s="16" t="inlineStr">
+      <c r="F86" s="16" t="inlineStr">
         <is>
           <t>Row 8 batch-size contract; pagination window</t>
         </is>
       </c>
-      <c r="F86" s="16" t="inlineStr">
+      <c r="G86" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -4136,20 +4552,25 @@
       </c>
       <c r="C87" s="15" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Email.xlsx</t>
+        </is>
+      </c>
+      <c r="D87" s="15" t="inlineStr">
+        <is>
           <t>TS-Email-CronPrune</t>
         </is>
       </c>
-      <c r="D87" s="15" t="inlineStr">
+      <c r="E87" s="15" t="inlineStr">
         <is>
           <t>EmailPruneScheduler — cron fires daily at 00:00, ShedLock acquired/released, start/finish markers emit</t>
         </is>
       </c>
-      <c r="E87" s="15" t="inlineStr">
+      <c r="F87" s="15" t="inlineStr">
         <is>
           <t>Row 9 happy-path; baseline retention scheduler</t>
         </is>
       </c>
-      <c r="F87" s="15" t="inlineStr">
+      <c r="G87" s="15" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -4168,20 +4589,25 @@
       </c>
       <c r="C88" s="16" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Email.xlsx</t>
+        </is>
+      </c>
+      <c r="D88" s="16" t="inlineStr">
+        <is>
           <t>TS-Email-CronPrune</t>
         </is>
       </c>
-      <c r="D88" s="16" t="inlineStr">
+      <c r="E88" s="16" t="inlineStr">
         <is>
           <t>Retention — emails older than 30 days deleted, emails newer than 30 days preserved</t>
         </is>
       </c>
-      <c r="E88" s="16" t="inlineStr">
+      <c r="F88" s="16" t="inlineStr">
         <is>
           <t>Row 9 retention baseline; PT30D cutoff</t>
         </is>
       </c>
-      <c r="F88" s="16" t="inlineStr">
+      <c r="G88" s="16" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
@@ -4200,20 +4626,25 @@
       </c>
       <c r="C89" s="15" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Email.xlsx</t>
+        </is>
+      </c>
+      <c r="D89" s="15" t="inlineStr">
+        <is>
           <t>TS-Email-CronPrune</t>
         </is>
       </c>
-      <c r="D89" s="15" t="inlineStr">
+      <c r="E89" s="15" t="inlineStr">
         <is>
           <t>Retention boundary — email exactly at 30-day cutoff behavior (strict less-than: &lt;30d preserved, =30d deleted)</t>
         </is>
       </c>
-      <c r="E89" s="15" t="inlineStr">
+      <c r="F89" s="15" t="inlineStr">
         <is>
           <t>Row 9 off-by-one guard on strict less-than ADD_TIME.lessThan</t>
         </is>
       </c>
-      <c r="F89" s="15" t="inlineStr">
+      <c r="G89" s="15" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -4232,20 +4663,25 @@
       </c>
       <c r="C90" s="16" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Email.xlsx</t>
+        </is>
+      </c>
+      <c r="D90" s="16" t="inlineStr">
+        <is>
           <t>TS-Email-CronPrune</t>
         </is>
       </c>
-      <c r="D90" s="16" t="inlineStr">
+      <c r="E90" s="16" t="inlineStr">
         <is>
           <t>Retention — attachments deleted with parent email (no FK orphans)</t>
         </is>
       </c>
-      <c r="E90" s="16" t="inlineStr">
+      <c r="F90" s="16" t="inlineStr">
         <is>
           <t>Row 9 cascade-delete contract; zero orphans</t>
         </is>
       </c>
-      <c r="F90" s="16" t="inlineStr">
+      <c r="G90" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -4264,27 +4700,32 @@
       </c>
       <c r="C91" s="15" t="inlineStr">
         <is>
+          <t>test-docs/collections/cron/Cron_Email.xlsx</t>
+        </is>
+      </c>
+      <c r="D91" s="15" t="inlineStr">
+        <is>
           <t>TS-Email-CronPrune</t>
         </is>
       </c>
-      <c r="D91" s="15" t="inlineStr">
+      <c r="E91" s="15" t="inlineStr">
         <is>
           <t>Retention no-op — all emails within retention window; finish marker reports 0 deleted</t>
         </is>
       </c>
-      <c r="E91" s="15" t="inlineStr">
+      <c r="F91" s="15" t="inlineStr">
         <is>
           <t>Row 9 no-op idempotency; zero-delete path</t>
         </is>
       </c>
-      <c r="F91" s="15" t="inlineStr">
+      <c r="G91" s="15" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F91"/>
+  <autoFilter ref="A4:G91"/>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A5:F5"/>
